--- a/fire_inspection_forms/004_fire_door_inspection_form--fire_inspection_forms.xlsx
+++ b/fire_inspection_forms/004_fire_door_inspection_form--fire_inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'fire_door_1',_'value':_'fire_door_1'}</t>
+          <t>fire_door_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'fire_door_1', 'value': 'fire_door_1'}</t>
+          <t>fire door 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fire_door_2',_'value':_'fire_door_2'}</t>
+          <t>fire_door_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'fire_door_2', 'value': 'fire_door_2'}</t>
+          <t>fire door 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'fire_alarm_system_1',_'value':_'fire_alarm_system_1'}</t>
+          <t>fire_alarm_system_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'fire_alarm_system_1', 'value': 'fire_alarm_system_1'}</t>
+          <t>fire alarm system 1</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fire_alarm_system_2',_'value':_'fire_alarm_system_2'}</t>
+          <t>fire_alarm_system_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'fire_alarm_system_2', 'value': 'fire_alarm_system_2'}</t>
+          <t>fire alarm system 2</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'fire_extinguisher_1',_'value':_'fire_extinguisher_1'}</t>
+          <t>fire_extinguisher_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'fire_extinguisher_1', 'value': 'fire_extinguisher_1'}</t>
+          <t>fire extinguisher 1</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fire_extinguisher_2',_'value':_'fire_extinguisher_2'}</t>
+          <t>fire_extinguisher_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'fire_extinguisher_2', 'value': 'fire_extinguisher_2'}</t>
+          <t>fire extinguisher 2</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'fire_alarm_testing_1',_'value':_'fire_alarm_testing_1'}</t>
+          <t>fire_alarm_testing_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'fire_alarm_testing_1', 'value': 'fire_alarm_testing_1'}</t>
+          <t>fire alarm testing 1</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fire_alarm_testing_2',_'value':_'fire_alarm_testing_2'}</t>
+          <t>fire_alarm_testing_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'fire_alarm_testing_2', 'value': 'fire_alarm_testing_2'}</t>
+          <t>fire alarm testing 2</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'quarterly',_'value':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'quarterly', 'value': 'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'semi_annually',_'value':_'semi_annually'}</t>
+          <t>semi_annually</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'semi_annually', 'value': 'semi_annually'}</t>
+          <t>semi annually</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'annually',_'value':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'annually', 'value': 'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'working',_'value':_'working'}</t>
+          <t>working</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'working', 'value': 'working'}</t>
+          <t>working</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'not_working',_'value':_'not_working'}</t>
+          <t>not_working</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'not_working', 'value': 'not_working'}</t>
+          <t>not working</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'passed',_'value':_'passed'}</t>
+          <t>passed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'passed', 'value': 'passed'}</t>
+          <t>passed</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'failed',_'value':_'failed'}</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'failed', 'value': 'failed'}</t>
+          <t>failed</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'pending', 'value': 'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'daily',_'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'daily', 'value': 'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'weekly',_'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'weekly', 'value': 'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'monthly',_'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'monthly', 'value': 'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'quarterly',_'value':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'quarterly', 'value': 'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'semi_annually',_'value':_'semi_annually'}</t>
+          <t>semi_annually</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'semi_annually', 'value': 'semi_annually'}</t>
+          <t>semi annually</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'annually',_'value':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'annually', 'value': 'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'fire_alarm_system_tested_1',_'value':_'fire_alarm_system_tested_1'}</t>
+          <t>fire_alarm_system_tested_1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'fire_alarm_system_tested_1', 'value': 'fire_alarm_system_tested_1'}</t>
+          <t>fire alarm system tested 1</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fire_alarm_system_tested_2',_'value':_'fire_alarm_system_tested_2'}</t>
+          <t>fire_alarm_system_tested_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'fire_alarm_system_tested_2', 'value': 'fire_alarm_system_tested_2'}</t>
+          <t>fire alarm system tested 2</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'fire_alarm_system_inspection_frequency_1',_'value':_'fire_alarm_system_inspection_frequency_1'}</t>
+          <t>fire_alarm_system_inspection_frequency_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'fire_alarm_system_inspection_frequency_1', 'value': 'fire_alarm_system_inspection_frequency_1'}</t>
+          <t>fire alarm system inspection frequency 1</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fire_alarm_system_inspection_frequency_2',_'value':_'fire_alarm_system_inspection_frequency_2'}</t>
+          <t>fire_alarm_system_inspection_frequency_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'fire_alarm_system_inspection_frequency_2', 'value': 'fire_alarm_system_inspection_frequency_2'}</t>
+          <t>fire alarm system inspection frequency 2</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'fire_alarm_system_inspection_status_1',_'value':_'fire_alarm_system_inspection_status_1'}</t>
+          <t>fire_alarm_system_inspection_status_1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'fire_alarm_system_inspection_status_1', 'value': 'fire_alarm_system_inspection_status_1'}</t>
+          <t>fire alarm system inspection status 1</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fire_alarm_system_inspection_status_2',_'value':_'fire_alarm_system_inspection_status_2'}</t>
+          <t>fire_alarm_system_inspection_status_2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'fire_alarm_system_inspection_status_2', 'value': 'fire_alarm_system_inspection_status_2'}</t>
+          <t>fire alarm system inspection status 2</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'active',_'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'active', 'value': 'active'}</t>
+          <t>active</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'inactive',_'value':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'inactive', 'value': 'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
     </row>
